--- a/convert/baocaovipham.xlsx
+++ b/convert/baocaovipham.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15952" uniqueCount="1535">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15933" uniqueCount="1535">
   <si>
     <t>2022-01-01</t>
   </si>
@@ -5281,8 +5281,8 @@
       <c r="AA10" t="s">
         <v>45</v>
       </c>
-      <c r="AK10" t="s">
-        <v>45</v>
+      <c r="AK10">
+        <v>120</v>
       </c>
       <c r="AV10">
         <v>56</v>
@@ -5438,8 +5438,8 @@
       <c r="AA12" t="s">
         <v>36</v>
       </c>
-      <c r="AK12" t="s">
-        <v>45</v>
+      <c r="AK12">
+        <v>120</v>
       </c>
       <c r="BG12" t="s">
         <v>36</v>
@@ -5743,8 +5743,8 @@
       <c r="AJ16">
         <v>4</v>
       </c>
-      <c r="AK16" t="s">
-        <v>45</v>
+      <c r="AK16">
+        <v>120</v>
       </c>
       <c r="BA16">
         <v>39</v>
@@ -13832,8 +13832,8 @@
       <c r="AE105" t="s">
         <v>45</v>
       </c>
-      <c r="AK105" t="s">
-        <v>45</v>
+      <c r="AK105">
+        <v>120</v>
       </c>
       <c r="AQ105">
         <v>29</v>
@@ -16188,8 +16188,8 @@
       <c r="AB131" t="s">
         <v>45</v>
       </c>
-      <c r="AK131" t="s">
-        <v>45</v>
+      <c r="AK131">
+        <v>120</v>
       </c>
       <c r="BL131">
         <v>24</v>
@@ -24178,8 +24178,8 @@
       <c r="AJ217">
         <v>4</v>
       </c>
-      <c r="AK217" t="s">
-        <v>45</v>
+      <c r="AK217">
+        <v>120</v>
       </c>
       <c r="BB217">
         <v>240</v>
@@ -28658,8 +28658,8 @@
       <c r="AJ267">
         <v>5</v>
       </c>
-      <c r="AK267" t="s">
-        <v>45</v>
+      <c r="AK267">
+        <v>120</v>
       </c>
       <c r="BF267">
         <v>61</v>
@@ -31136,8 +31136,8 @@
       <c r="AJ294">
         <v>5</v>
       </c>
-      <c r="AK294" t="s">
-        <v>45</v>
+      <c r="AK294">
+        <v>120</v>
       </c>
       <c r="AL294">
         <v>59</v>
@@ -34175,8 +34175,8 @@
       <c r="AB327">
         <v>1</v>
       </c>
-      <c r="AK327" t="s">
-        <v>45</v>
+      <c r="AK327">
+        <v>120</v>
       </c>
       <c r="AT327">
         <v>1</v>
@@ -34810,8 +34810,8 @@
       <c r="AJ334">
         <v>4</v>
       </c>
-      <c r="AK334" t="s">
-        <v>45</v>
+      <c r="AK334">
+        <v>120</v>
       </c>
       <c r="AN334">
         <v>354</v>
@@ -36709,8 +36709,8 @@
       <c r="AJ355">
         <v>4</v>
       </c>
-      <c r="AK355" t="s">
-        <v>45</v>
+      <c r="AK355">
+        <v>120</v>
       </c>
       <c r="BL355">
         <v>53</v>
@@ -39665,8 +39665,8 @@
       <c r="AB387">
         <v>1</v>
       </c>
-      <c r="AK387" t="s">
-        <v>45</v>
+      <c r="AK387">
+        <v>120</v>
       </c>
       <c r="AT387">
         <v>239</v>
@@ -42040,8 +42040,8 @@
       <c r="BJ415">
         <v>2</v>
       </c>
-      <c r="BK415" t="s">
-        <v>45</v>
+      <c r="BK415">
+        <v>120</v>
       </c>
       <c r="BL415">
         <v>25</v>
@@ -47133,8 +47133,8 @@
       <c r="AJ473">
         <v>1</v>
       </c>
-      <c r="AK473" t="s">
-        <v>45</v>
+      <c r="AK473">
+        <v>120</v>
       </c>
       <c r="BH473">
         <v>1</v>
@@ -48254,8 +48254,8 @@
       <c r="AJ486">
         <v>1</v>
       </c>
-      <c r="AK486" t="s">
-        <v>45</v>
+      <c r="AK486">
+        <v>120</v>
       </c>
       <c r="AL486">
         <v>82</v>
@@ -51133,8 +51133,8 @@
       <c r="AB517">
         <v>1</v>
       </c>
-      <c r="AK517" t="s">
-        <v>45</v>
+      <c r="AK517">
+        <v>120</v>
       </c>
       <c r="AL517">
         <v>59</v>
@@ -53411,8 +53411,8 @@
       <c r="AA543" t="s">
         <v>36</v>
       </c>
-      <c r="AK543" t="s">
-        <v>45</v>
+      <c r="AK543">
+        <v>120</v>
       </c>
       <c r="AL543">
         <v>65</v>
@@ -55446,8 +55446,8 @@
       <c r="BJ566">
         <v>3</v>
       </c>
-      <c r="BK566" t="s">
-        <v>45</v>
+      <c r="BK566">
+        <v>120</v>
       </c>
       <c r="BL566">
         <v>16</v>
@@ -55983,8 +55983,8 @@
       <c r="AJ572">
         <v>2</v>
       </c>
-      <c r="AK572" t="s">
-        <v>45</v>
+      <c r="AK572">
+        <v>120</v>
       </c>
       <c r="AL572">
         <v>86</v>
